--- a/data/trending_integrated_20260923_13.xlsx
+++ b/data/trending_integrated_20260923_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4305</v>
+        <v>4120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.86%</t>
+          <t>'+24.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31620925298</v>
+        <v>33985775176</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18180</v>
+        <v>1956</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.14%</t>
+          <t>'+22.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.5</v>
+        <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>301</v>
+        <v>116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15520</v>
+        <v>1603</v>
       </c>
       <c r="K3" t="n">
-        <v>15800</v>
+        <v>1603</v>
       </c>
       <c r="L3" t="n">
-        <v>19150</v>
+        <v>2030</v>
       </c>
       <c r="M3" t="n">
-        <v>15200</v>
+        <v>1585</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>85166205915</v>
+        <v>47430068304</v>
       </c>
       <c r="P3" t="n">
-        <v>34650</v>
+        <v>2465</v>
       </c>
       <c r="Q3" t="n">
-        <v>6980</v>
+        <v>865</v>
       </c>
       <c r="R3" t="n">
-        <v>2000</v>
+        <v>72000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 인도발 수주 등 강력한 호재와 함께 11조원 규모의 시장 도전에 대한 기대감이 고조되고 있으며, 공매도 세력에 대한 압박이 커지고 있음.</t>
+          <t>미국 특허 기반 AI 데이터센터향 플렉시블 PCB 공급 확대에 따른 급등 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', '수주']</t>
+          <t>['플렉시블PCB', 'AI데이터센터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14440</v>
+        <v>15850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.08%</t>
+          <t>'+21.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>13030</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12850</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16420</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12660</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O4" t="n">
+        <v>86217308185</v>
+      </c>
+      <c r="P4" t="n">
+        <v>64600</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7520</v>
+      </c>
+      <c r="R4" t="n">
         <v>13000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12870</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15900</v>
-      </c>
-      <c r="M4" t="n">
-        <v>12650</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O4" t="n">
-        <v>155163182725</v>
-      </c>
-      <c r="P4" t="n">
-        <v>25700</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4600</v>
-      </c>
-      <c r="R4" t="n">
-        <v>95000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형 위성 국방 과제 수주 및 투자경고 지정에 따른 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['초소형위성', '투자경고']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18120</v>
+        <v>18100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.55%</t>
+          <t>'+16.62%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F5" t="n">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16540</v>
+        <v>15520</v>
       </c>
       <c r="K5" t="n">
-        <v>17530</v>
+        <v>15800</v>
       </c>
       <c r="L5" t="n">
-        <v>19950</v>
+        <v>19150</v>
       </c>
       <c r="M5" t="n">
-        <v>17500</v>
+        <v>15200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>290540192000</v>
+        <v>85758630525</v>
       </c>
       <c r="P5" t="n">
-        <v>30550</v>
+        <v>34650</v>
       </c>
       <c r="Q5" t="n">
-        <v>6100</v>
+        <v>6980</v>
       </c>
       <c r="R5" t="n">
-        <v>-46000</v>
+        <v>2000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>양자 보안 관련 미 증시 급등에 따른 기대감과 주가 변동성.</t>
+          <t>스페이스X 선정 및 NASA 협업 기반 휴대용 X-Ray 시장 확대에 따른 급등 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '아이온큐', '공매도']</t>
+          <t>['X-Ray', '스페이스X']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218500</v>
+        <v>14500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+11.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>340</v>
+        <v>97</v>
       </c>
       <c r="H6" t="n">
-        <v>75.51000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>211500</v>
+        <v>13000</v>
       </c>
       <c r="K6" t="n">
-        <v>217000</v>
+        <v>12870</v>
       </c>
       <c r="L6" t="n">
-        <v>220000</v>
+        <v>15900</v>
       </c>
       <c r="M6" t="n">
-        <v>216500</v>
+        <v>12650</v>
       </c>
       <c r="N6" t="n">
-        <v>75.5</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>741549464750</v>
+        <v>156612512515</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>25700</v>
       </c>
       <c r="Q6" t="n">
-        <v>65000</v>
+        <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>753000</v>
+        <v>95000</v>
       </c>
       <c r="S6" t="n">
-        <v>-47000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '장기보유']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14020</v>
+        <v>17950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.09%</t>
+          <t>'+8.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>163</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
-        <v>203</v>
+        <v>282</v>
       </c>
       <c r="H7" t="n">
-        <v>9.609999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13600</v>
+        <v>16540</v>
       </c>
       <c r="K7" t="n">
-        <v>13750</v>
+        <v>17530</v>
       </c>
       <c r="L7" t="n">
-        <v>15050</v>
+        <v>19950</v>
       </c>
       <c r="M7" t="n">
-        <v>13740</v>
+        <v>17500</v>
       </c>
       <c r="N7" t="n">
-        <v>9.77</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>94223760850</v>
+        <v>293402991325</v>
       </c>
       <c r="P7" t="n">
-        <v>23550</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>5780</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>180000</v>
+        <v>-46000</v>
       </c>
       <c r="S7" t="n">
-        <v>-194000</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>양자 보안 관련 미 증시 급등에 따른 기대감과 주가 변동성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['양자보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,95 +1103,95 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>283250</v>
+        <v>7930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+4.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>483</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>1893</v>
+        <v>282</v>
       </c>
       <c r="H8" t="n">
-        <v>46.55</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276500</v>
+        <v>7610</v>
       </c>
       <c r="K8" t="n">
-        <v>284500</v>
+        <v>7850</v>
       </c>
       <c r="L8" t="n">
-        <v>285000</v>
+        <v>8720</v>
       </c>
       <c r="M8" t="n">
-        <v>281000</v>
+        <v>7730</v>
       </c>
       <c r="N8" t="n">
-        <v>46.56</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>3056930010750</v>
+        <v>85664286665</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>82400</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>1744000</v>
+        <v>61000</v>
       </c>
       <c r="S8" t="n">
-        <v>499000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치 관련 언급 다수, 일부 매수/매도 의견 혼재.</t>
+          <t>주가 변동성에 대한 혼란과 기대감이 혼재된 의견.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가', '매매']</t>
+          <t>['양자', '빛샘']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,130 +1200,130 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3810</v>
+        <v>219000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.28%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.35</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="H9" t="n">
-        <v>0.61</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3725</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>3740</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>4200</v>
+        <v>220000</v>
       </c>
       <c r="M9" t="n">
-        <v>3705</v>
+        <v>216500</v>
       </c>
       <c r="N9" t="n">
-        <v>0.96</v>
+        <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>64450272312</v>
+        <v>753114430500</v>
       </c>
       <c r="P9" t="n">
-        <v>6300</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1738</v>
+        <v>65000</v>
       </c>
       <c r="R9" t="n">
-        <v>-41000</v>
+        <v>753000</v>
       </c>
       <c r="S9" t="n">
-        <v>-5000</v>
+        <v>-31000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 의혹 제기.</t>
+          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주가하락', '물량', '상폐']</t>
+          <t>['배당', '우선주', '장기보유']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8510</v>
+        <v>14000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.05</v>
+        <v>-0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="H10" t="n">
-        <v>26.63</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8470</v>
+        <v>13600</v>
       </c>
       <c r="K10" t="n">
-        <v>8510</v>
+        <v>13750</v>
       </c>
       <c r="L10" t="n">
-        <v>8870</v>
+        <v>15050</v>
       </c>
       <c r="M10" t="n">
-        <v>8480</v>
+        <v>13740</v>
       </c>
       <c r="N10" t="n">
-        <v>26.58</v>
+        <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>21526696885</v>
+        <v>94861119750</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>23550</v>
       </c>
       <c r="Q10" t="n">
-        <v>8120</v>
+        <v>5780</v>
       </c>
       <c r="R10" t="n">
-        <v>353000</v>
+        <v>180000</v>
       </c>
       <c r="S10" t="n">
-        <v>-6000</v>
+        <v>-397000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>키움증권의 매수·매도 공방 속에서 주가 상승 기대감과 함께 '물량 넘기기', '가짜 외인' 등 의혹이 제기됨. 유리 기판 사업 등 신사업에 대한 언급도 있음.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['매매주체', '실적', '신사업']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1844000</v>
+        <v>284500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="G11" t="n">
-        <v>1704</v>
+        <v>1886</v>
       </c>
       <c r="H11" t="n">
-        <v>50.15</v>
+        <v>46.55</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1840000</v>
+        <v>276500</v>
       </c>
       <c r="K11" t="n">
-        <v>1899000</v>
+        <v>284500</v>
       </c>
       <c r="L11" t="n">
-        <v>1900000</v>
+        <v>285000</v>
       </c>
       <c r="M11" t="n">
-        <v>1836000</v>
+        <v>281000</v>
       </c>
       <c r="N11" t="n">
-        <v>50.17</v>
+        <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3516929641500</v>
+        <v>3244855226250</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>333000</v>
+        <v>82400</v>
       </c>
       <c r="R11" t="n">
-        <v>-103000</v>
+        <v>1744000</v>
       </c>
       <c r="S11" t="n">
-        <v>106000</v>
+        <v>499000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 및 하이닉스 주가 관리 방식에 대한 불신과 부정적 전망.</t>
+          <t>정치적 언급과 주가 관련 기대가 혼재된 의견.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가조작', '레버리지', '외국인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,182 +1476,182 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31350</v>
+        <v>3770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.16%</t>
+          <t>'+1.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>-0.35</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>387</v>
       </c>
       <c r="H12" t="n">
-        <v>52.8</v>
+        <v>0.61</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31400</v>
+        <v>3725</v>
       </c>
       <c r="K12" t="n">
-        <v>31500</v>
+        <v>3740</v>
       </c>
       <c r="L12" t="n">
-        <v>32100</v>
+        <v>4200</v>
       </c>
       <c r="M12" t="n">
-        <v>31100</v>
+        <v>3705</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>0.96</v>
       </c>
       <c r="O12" t="n">
-        <v>88883433075</v>
+        <v>64816662272</v>
       </c>
       <c r="P12" t="n">
-        <v>32100</v>
+        <v>6300</v>
       </c>
       <c r="Q12" t="n">
-        <v>21000</v>
+        <v>1738</v>
       </c>
       <c r="R12" t="n">
-        <v>-6000</v>
+        <v>-41000</v>
       </c>
       <c r="S12" t="n">
-        <v>51000</v>
+        <v>-5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['주가하락', '물량', '상폐']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17640</v>
+        <v>1852000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'+0.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.76</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="G13" t="n">
-        <v>789</v>
+        <v>1700</v>
       </c>
       <c r="H13" t="n">
-        <v>5.46</v>
+        <v>50.15</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17810</v>
+        <v>1840000</v>
       </c>
       <c r="K13" t="n">
-        <v>17950</v>
+        <v>1899000</v>
       </c>
       <c r="L13" t="n">
-        <v>18180</v>
+        <v>1900000</v>
       </c>
       <c r="M13" t="n">
-        <v>17410</v>
+        <v>1836000</v>
       </c>
       <c r="N13" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="O13" t="n">
-        <v>125089592465</v>
+        <v>3595945651500</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>-260000</v>
+        <v>-103000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
+          <t>주가 관리 및 국장 불신에 대한 불만이 강하게 표출된 의견.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가', '명절', '단타']</t>
+          <t>['반도체', '국장']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30700</v>
+        <v>8510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>276</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>1726</v>
+        <v>328</v>
       </c>
       <c r="H14" t="n">
-        <v>16.63</v>
+        <v>26.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31050</v>
+        <v>8470</v>
       </c>
       <c r="K14" t="n">
-        <v>31300</v>
+        <v>8510</v>
       </c>
       <c r="L14" t="n">
-        <v>31550</v>
+        <v>8870</v>
       </c>
       <c r="M14" t="n">
-        <v>30050</v>
+        <v>8480</v>
       </c>
       <c r="N14" t="n">
-        <v>16.42</v>
+        <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>9743348125</v>
+        <v>21755434580</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>353000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-29000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>간암 신약 FDA 허가 임박 및 리보세라닙 승인 기대감.</t>
+          <t>주가 부양을 위한 세력 개입 의혹과 유리 기판 사업 성장 전망이 혼재된 의견.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '간암']</t>
+          <t>['유리기판', '디스플레이']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>31400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="H15" t="n">
-        <v>11.7</v>
+        <v>52.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>31600</v>
+        <v>31400</v>
       </c>
       <c r="K15" t="n">
-        <v>32150</v>
+        <v>31500</v>
       </c>
       <c r="L15" t="n">
-        <v>32200</v>
+        <v>32100</v>
       </c>
       <c r="M15" t="n">
-        <v>30550</v>
+        <v>31100</v>
       </c>
       <c r="N15" t="n">
-        <v>11.3</v>
+        <v>25.75</v>
       </c>
       <c r="O15" t="n">
-        <v>70838760925</v>
+        <v>90215923575</v>
       </c>
       <c r="P15" t="n">
-        <v>75900</v>
+        <v>32100</v>
       </c>
       <c r="Q15" t="n">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="R15" t="n">
-        <v>-496000</v>
+        <v>-6000</v>
       </c>
       <c r="S15" t="n">
-        <v>-31000</v>
+        <v>107000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['구리', '텍사스', '가온전선']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23150</v>
+        <v>30750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-0.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>1790</v>
       </c>
       <c r="H16" t="n">
-        <v>1.68</v>
+        <v>16.63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23950</v>
+        <v>31050</v>
       </c>
       <c r="K16" t="n">
-        <v>24400</v>
+        <v>31300</v>
       </c>
       <c r="L16" t="n">
-        <v>25700</v>
+        <v>31550</v>
       </c>
       <c r="M16" t="n">
-        <v>23050</v>
+        <v>30050</v>
       </c>
       <c r="N16" t="n">
-        <v>1.76</v>
+        <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>67982897900</v>
+        <v>10011062625</v>
       </c>
       <c r="P16" t="n">
-        <v>39350</v>
+        <v>69200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8200</v>
+        <v>24150</v>
       </c>
       <c r="R16" t="n">
-        <v>-39000</v>
+        <v>-51000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 기업으로 높은 기대감을 보이나, 거래량 소멸과 변동성 속에서 추세 전환 여부에 대한 관심이 집중되고 있음.</t>
+          <t>간암 및 담관암 신약 FDA 허가 임박에 따른 주가 급등 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['타임지', '추세선', '거래량']</t>
+          <t>['간암', 'FDA']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48750</v>
+        <v>17630</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-1.01%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>196</v>
+        <v>793</v>
       </c>
       <c r="H17" t="n">
-        <v>38.34</v>
+        <v>5.46</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>51200</v>
+        <v>17810</v>
       </c>
       <c r="K17" t="n">
-        <v>51600</v>
+        <v>17950</v>
       </c>
       <c r="L17" t="n">
-        <v>51600</v>
+        <v>18180</v>
       </c>
       <c r="M17" t="n">
-        <v>48600</v>
+        <v>17410</v>
       </c>
       <c r="N17" t="n">
-        <v>38.44</v>
+        <v>6.22</v>
       </c>
       <c r="O17" t="n">
-        <v>74479133650</v>
+        <v>125815238010</v>
       </c>
       <c r="P17" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>23150</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-262000</v>
+        <v>-260000</v>
       </c>
       <c r="S17" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 6개월간의 보유 기간에 대한 회의감.</t>
+          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가하락', '20일선', '보유']</t>
+          <t>['주가', '명절', '단타']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,182 +2028,182 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2730</v>
+        <v>30900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4</v>
+        <v>11.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2885</v>
+        <v>31600</v>
       </c>
       <c r="K18" t="n">
-        <v>3000</v>
+        <v>32150</v>
       </c>
       <c r="L18" t="n">
-        <v>3480</v>
+        <v>32200</v>
       </c>
       <c r="M18" t="n">
-        <v>2685</v>
+        <v>30550</v>
       </c>
       <c r="N18" t="n">
-        <v>0.48</v>
+        <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>21868121167</v>
+        <v>71528649375</v>
       </c>
       <c r="P18" t="n">
-        <v>4760</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>973</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-227000</v>
+        <v>-496000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-39000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>잦은 유상증자와 경영권 변경에 대한 부정적 시각 및 주가 우려.</t>
+          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유상증자', '경영권변경', '주가']</t>
+          <t>['구리', '텍사스', '가온전선']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81300</v>
+        <v>23050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-3.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
-        <v>338</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>1733</v>
+        <v>111</v>
       </c>
       <c r="H19" t="n">
-        <v>23.03</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>86500</v>
+        <v>23950</v>
       </c>
       <c r="K19" t="n">
-        <v>86100</v>
+        <v>24400</v>
       </c>
       <c r="L19" t="n">
-        <v>86100</v>
+        <v>25700</v>
       </c>
       <c r="M19" t="n">
-        <v>80500</v>
+        <v>23050</v>
       </c>
       <c r="N19" t="n">
-        <v>23.05</v>
+        <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>258255880650</v>
+        <v>68259160450</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>39350</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>8200</v>
       </c>
       <c r="R19" t="n">
-        <v>-486000</v>
+        <v>-39000</v>
       </c>
       <c r="S19" t="n">
-        <v>-68000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 사업 관련 호재에도 불구하고 주가 하락 및 부정적 전망.</t>
+          <t>타임지 선정 기업으로 높은 기대감을 보이나, 거래량 소멸과 변동성 속에서 추세 전환 여부에 대한 관심이 집중되고 있음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가하락']</t>
+          <t>['타임지', '추세선', '거래량']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17510</v>
+        <v>48775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.86%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>230</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>931</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>10.38</v>
+        <v>38.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,58 +2251,334 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>18800</v>
+        <v>51200</v>
       </c>
       <c r="K20" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="L20" t="n">
-        <v>18800</v>
+        <v>51600</v>
       </c>
       <c r="M20" t="n">
-        <v>17370</v>
+        <v>48600</v>
       </c>
       <c r="N20" t="n">
-        <v>10.47</v>
+        <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>127202414315</v>
+        <v>75246512450</v>
       </c>
       <c r="P20" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q20" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R20" t="n">
-        <v>-1898000</v>
+        <v>-262000</v>
       </c>
       <c r="S20" t="n">
-        <v>-250000</v>
+        <v>-30000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 및 마지막 몸부림에 대한 언급 다수.</t>
+          <t>주가 하락에 대한 불만과 6개월간의 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['주가하락', '20일선', '보유']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>셀리드</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2725</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-5.55%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E21" t="n">
+        <v>89</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>203</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2885</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3480</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2685</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O21" t="n">
+        <v>21985687662</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4760</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>973</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-227000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>유상증자 및 경영권 변경에 대한 불신과 항암 백신 사업에 대한 기대가 혼재된 의견.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['유상증자', '항암백신']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>299660</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>81400</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-5.90%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E22" t="n">
+        <v>605</v>
+      </c>
+      <c r="F22" t="n">
+        <v>341</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1757</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>86500</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86100</v>
+      </c>
+      <c r="L22" t="n">
+        <v>86100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>80500</v>
+      </c>
+      <c r="N22" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>263222416150</v>
+      </c>
+      <c r="P22" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-486000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-179000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>미국향 원전 수주 기대와 주가 하락에 대한 불만이 혼재된 의견.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['원전', 'SMR']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>17530</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-6.76%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E23" t="n">
+        <v>233</v>
+      </c>
+      <c r="F23" t="n">
+        <v>109</v>
+      </c>
+      <c r="G23" t="n">
+        <v>954</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>18800</v>
+      </c>
+      <c r="K23" t="n">
+        <v>18800</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18800</v>
+      </c>
+      <c r="M23" t="n">
+        <v>17370</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O23" t="n">
+        <v>128390120705</v>
+      </c>
+      <c r="P23" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-1898000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>공매도 세력의 파산 및 마지막 몸부림에 대한 언급 다수.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>0.3</v>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>['공매도', '대차', '주가조작']</t>
         </is>
       </c>
-      <c r="X20" t="n">
+      <c r="X23" t="n">
         <v>22</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260923_13.xlsx
+++ b/data/trending_integrated_20260923_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4120</v>
+        <v>4080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.28%</t>
+          <t>'+23.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>33985775176</v>
+        <v>36834827423</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1956</v>
+        <v>1943</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.02%</t>
+          <t>'+21.21%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H3" t="n">
         <v>1.02</v>
@@ -702,7 +702,7 @@
         <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>47430068304</v>
+        <v>49852945800</v>
       </c>
       <c r="P3" t="n">
         <v>2465</v>
@@ -711,23 +711,23 @@
         <v>865</v>
       </c>
       <c r="R3" t="n">
-        <v>72000</v>
+        <v>-358000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 특허 기반 AI 데이터센터향 플렉시블 PCB 공급 확대에 따른 급등 전망.</t>
+          <t>삼기에너지솔루션즈의 미국 특허 플렉시블 PCB, AI 데이터센터 공급 확대 뉴스 언급. ESS 및 NVIDIA 관련 기대감 표출.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['플렉시블PCB', 'AI데이터센터']</t>
+          <t>['플렉시블 PCB', 'AI 데이터센터', '미국 특허']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15850</v>
+        <v>15470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.64%</t>
+          <t>'+18.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -794,7 +794,7 @@
         <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>86217308185</v>
+        <v>94222385810</v>
       </c>
       <c r="P4" t="n">
         <v>64600</v>
@@ -803,14 +803,14 @@
         <v>7520</v>
       </c>
       <c r="R4" t="n">
-        <v>13000</v>
+        <v>2000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>초소형 위성 국방 과제 수주 및 투자경고 지정에 따른 주가 급등 기대.</t>
+          <t>초소형위성 자율 근접운영 국방과제 주관 및 67억원 규모 계약 체결. 테마 시작 기대감 속 단일가 매매 여부에 따른 주가 변동성 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['초소형위성', '투자경고']</t>
+          <t>['초소형위성', '국방과제', '단일가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18100</v>
+        <v>17720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.62%</t>
+          <t>'+14.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="H5" t="n">
         <v>0.6</v>
@@ -886,7 +886,7 @@
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>85758630525</v>
+        <v>87502904515</v>
       </c>
       <c r="P5" t="n">
         <v>34650</v>
@@ -895,14 +895,14 @@
         <v>6980</v>
       </c>
       <c r="R5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 선정 및 NASA 협업 기반 휴대용 X-Ray 시장 확대에 따른 급등 전망.</t>
+          <t>스페이스X 및 NASA 선정, 11조원 포터블 X-Ray 시장 도전. 인도발 수주 및 미국, 인도, 인도네시아 시장 진출 재료로 인한 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['X-Ray', '스페이스X']</t>
+          <t>['X-Ray', '스페이스X', 'NASA']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14500</v>
+        <v>14530</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.54%</t>
+          <t>'+11.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,7 +949,7 @@
         <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
         <v>97</v>
@@ -978,7 +978,7 @@
         <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>156612512515</v>
+        <v>157856778230</v>
       </c>
       <c r="P6" t="n">
         <v>25700</v>
@@ -987,7 +987,7 @@
         <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>95000</v>
+        <v>84000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17950</v>
+        <v>18000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.52%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G7" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>293402991325</v>
+        <v>296485911605</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1079,14 +1079,14 @@
         <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-46000</v>
+        <v>-77000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>양자 보안 관련 미 증시 급등에 따른 기대감과 주가 변동성.</t>
+          <t>미국 양자 관련주 급등 소식과 함께 엑스게이트의 양자 보안 관련 기대감 표현. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자보안', '아이온큐', '공매도']</t>
+          <t>['양자 보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7930</v>
+        <v>7890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.20%</t>
+          <t>'+3.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="H8" t="n">
         <v>1.9</v>
@@ -1162,7 +1162,7 @@
         <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>85664286665</v>
+        <v>86668943535</v>
       </c>
       <c r="P8" t="n">
         <v>16200</v>
@@ -1171,23 +1171,23 @@
         <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>61000</v>
+        <v>-26000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 변동성에 대한 혼란과 기대감이 혼재된 의견.</t>
+          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자', '빛샘']</t>
+          <t>['계단식 하락', '매물대', '외인 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H9" t="n">
         <v>75.51000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>753114430500</v>
+        <v>773500417750</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1263,10 +1263,10 @@
         <v>65000</v>
       </c>
       <c r="R9" t="n">
-        <v>753000</v>
+        <v>605000</v>
       </c>
       <c r="S9" t="n">
-        <v>-31000</v>
+        <v>-57000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14000</v>
+        <v>13980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>94861119750</v>
+        <v>95402332020</v>
       </c>
       <c r="P10" t="n">
         <v>23550</v>
@@ -1355,7 +1355,7 @@
         <v>5780</v>
       </c>
       <c r="R10" t="n">
-        <v>180000</v>
+        <v>211000</v>
       </c>
       <c r="S10" t="n">
         <v>-397000</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>284500</v>
+        <v>283500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G11" t="n">
-        <v>1886</v>
+        <v>1847</v>
       </c>
       <c r="H11" t="n">
         <v>46.55</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3244855226250</v>
+        <v>3324488136500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1447,10 +1447,10 @@
         <v>82400</v>
       </c>
       <c r="R11" t="n">
-        <v>1744000</v>
+        <v>1963000</v>
       </c>
       <c r="S11" t="n">
-        <v>499000</v>
+        <v>599000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3770</v>
+        <v>1854000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.21%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.35</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>138</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>493</v>
       </c>
       <c r="G12" t="n">
-        <v>387</v>
+        <v>1737</v>
       </c>
       <c r="H12" t="n">
-        <v>0.61</v>
+        <v>50.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3725</v>
+        <v>1840000</v>
       </c>
       <c r="K12" t="n">
-        <v>3740</v>
+        <v>1899000</v>
       </c>
       <c r="L12" t="n">
-        <v>4200</v>
+        <v>1900000</v>
       </c>
       <c r="M12" t="n">
-        <v>3705</v>
+        <v>1836000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.96</v>
+        <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>64816662272</v>
+        <v>3670862977500</v>
       </c>
       <c r="P12" t="n">
-        <v>6300</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>1738</v>
+        <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>-41000</v>
+        <v>-289000</v>
       </c>
       <c r="S12" t="n">
-        <v>-5000</v>
+        <v>78000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 의혹 제기.</t>
+          <t>국내 주식 시장의 신뢰 부족 및 정부 정책 비판. 미국 반도체 주가와 비교하며 SK하이닉스 주가 하락에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가하락', '물량', '상폐']</t>
+          <t>['국장', '정부 정책', '주가 조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1852000</v>
+        <v>8530</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.65%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="F13" t="n">
-        <v>492</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>1700</v>
+        <v>334</v>
       </c>
       <c r="H13" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K13" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L13" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M13" t="n">
-        <v>1836000</v>
+        <v>8480</v>
       </c>
       <c r="N13" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>3595945651500</v>
+        <v>22140012950</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-103000</v>
+        <v>275000</v>
       </c>
       <c r="S13" t="n">
-        <v>78000</v>
+        <v>-45000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 관리 및 국장 불신에 대한 불만이 강하게 표출된 의견.</t>
+          <t>LG디스플레이 유리기판 사업 및 게이밍 OLED 관련 신규 기술 언급. 일부 투자자 매수세 유입 및 목표가 상향 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '국장']</t>
+          <t>['유리기판', 'OLED', '커스텀 공정']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8510</v>
+        <v>31450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>328</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
-        <v>26.63</v>
+        <v>52.79</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,130 +1699,130 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>31400</v>
       </c>
       <c r="K14" t="n">
-        <v>8510</v>
+        <v>31500</v>
       </c>
       <c r="L14" t="n">
-        <v>8870</v>
+        <v>32100</v>
       </c>
       <c r="M14" t="n">
-        <v>8480</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58</v>
+        <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>21755434580</v>
+        <v>91646878075</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>32100</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R14" t="n">
-        <v>353000</v>
+        <v>-37000</v>
       </c>
       <c r="S14" t="n">
-        <v>-29000</v>
+        <v>174000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 부양을 위한 세력 개입 의혹과 유리 기판 사업 성장 전망이 혼재된 의견.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유리기판', '디스플레이']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31400</v>
+        <v>3720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.62</v>
+        <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>145</v>
+        <v>398</v>
       </c>
       <c r="H15" t="n">
-        <v>52.8</v>
+        <v>0.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>31400</v>
+        <v>3725</v>
       </c>
       <c r="K15" t="n">
-        <v>31500</v>
+        <v>3740</v>
       </c>
       <c r="L15" t="n">
-        <v>32100</v>
+        <v>4200</v>
       </c>
       <c r="M15" t="n">
-        <v>31100</v>
+        <v>3705</v>
       </c>
       <c r="N15" t="n">
-        <v>25.75</v>
+        <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>90215923575</v>
+        <v>65719682972</v>
       </c>
       <c r="P15" t="n">
-        <v>32100</v>
+        <v>6300</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-6000</v>
+        <v>-191000</v>
       </c>
       <c r="S15" t="n">
-        <v>107000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>미투온의 급격한 주가 하락 및 물량 떠넘기기에 대한 불만 표출. 상폐 가능성 및 국장 단타장 변질 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,51 +1831,51 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['물량 떠넘기기', '주포', '단타장']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30750</v>
+        <v>17630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-1.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="F16" t="n">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>1790</v>
+        <v>795</v>
       </c>
       <c r="H16" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K16" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L16" t="n">
-        <v>31550</v>
+        <v>18180</v>
       </c>
       <c r="M16" t="n">
-        <v>30050</v>
+        <v>17410</v>
       </c>
       <c r="N16" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>10011062625</v>
+        <v>126699681050</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-51000</v>
+        <v>-215000</v>
       </c>
       <c r="S16" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>간암 및 담관암 신약 FDA 허가 임박에 따른 주가 급등 기대.</t>
+          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['간암', 'FDA']</t>
+          <t>['주가', '명절', '단타']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17630</v>
+        <v>30650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>285</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="G17" t="n">
-        <v>793</v>
+        <v>1830</v>
       </c>
       <c r="H17" t="n">
-        <v>5.46</v>
+        <v>16.63</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17810</v>
+        <v>31050</v>
       </c>
       <c r="K17" t="n">
-        <v>17950</v>
+        <v>31300</v>
       </c>
       <c r="L17" t="n">
-        <v>18180</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>17410</v>
+        <v>30050</v>
       </c>
       <c r="N17" t="n">
-        <v>6.22</v>
+        <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>125815238010</v>
+        <v>10237071875</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-260000</v>
+        <v>-88000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
+          <t>간암 및 담관암 신약 FDA 허가 초임박 소식과 함께 미국 릴레이테라퓨틱스 상승. 다만, CRL 가능성 및 공매도 이슈로 인한 주가 변동성 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가', '명절', '단타']</t>
+          <t>['FDA허가', '신약', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2039,18 +2039,18 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30900</v>
+        <v>30950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>42</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>71528649375</v>
+        <v>72411223200</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2091,7 +2091,7 @@
         <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-496000</v>
+        <v>-681000</v>
       </c>
       <c r="S18" t="n">
         <v>-39000</v>
@@ -2142,13 +2142,13 @@
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H19" t="n">
         <v>1.68</v>
@@ -2168,13 +2168,13 @@
         <v>25700</v>
       </c>
       <c r="M19" t="n">
-        <v>23050</v>
+        <v>23000</v>
       </c>
       <c r="N19" t="n">
         <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>68259160450</v>
+        <v>68849310150</v>
       </c>
       <c r="P19" t="n">
         <v>39350</v>
@@ -2183,23 +2183,23 @@
         <v>8200</v>
       </c>
       <c r="R19" t="n">
-        <v>-39000</v>
+        <v>-53000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>타임지 선정 기업으로 높은 기대감을 보이나, 거래량 소멸과 변동성 속에서 추세 전환 여부에 대한 관심이 집중되고 있음.</t>
+          <t>타임지 세계 최고 헬스테크 기업 선정 및 반지 재료 부각. 매수세 부진과 거래량 감소 속 추세선에 따른 방향성 결정 예상.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['타임지', '추세선', '거래량']</t>
+          <t>['헬스테크', '타임지', '반지']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48775</v>
+        <v>48850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F20" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H20" t="n">
         <v>38.34</v>
@@ -2266,7 +2266,7 @@
         <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>75246512450</v>
+        <v>76142670250</v>
       </c>
       <c r="P20" t="n">
         <v>67300</v>
@@ -2275,14 +2275,14 @@
         <v>23150</v>
       </c>
       <c r="R20" t="n">
-        <v>-262000</v>
+        <v>-327000</v>
       </c>
       <c r="S20" t="n">
         <v>-30000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 6개월간의 보유 기간에 대한 회의감.</t>
+          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주가하락', '20일선', '보유']</t>
+          <t>['20일선', '주가 하락', 'MSCI']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2725</v>
+        <v>81400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.55%</t>
+          <t>'-5.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.92</v>
+        <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>89</v>
+        <v>614</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>344</v>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>1779</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4</v>
+        <v>23.03</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2885</v>
+        <v>86500</v>
       </c>
       <c r="K21" t="n">
-        <v>3000</v>
+        <v>86100</v>
       </c>
       <c r="L21" t="n">
-        <v>3480</v>
+        <v>86100</v>
       </c>
       <c r="M21" t="n">
-        <v>2685</v>
+        <v>80500</v>
       </c>
       <c r="N21" t="n">
-        <v>0.48</v>
+        <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>21985687662</v>
+        <v>268387419700</v>
       </c>
       <c r="P21" t="n">
-        <v>4760</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>973</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-227000</v>
+        <v>-1068000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-190000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>유상증자 및 경영권 변경에 대한 불신과 항암 백신 사업에 대한 기대가 혼재된 의견.</t>
+          <t>미국 한국형 원전 2기 확정 소식 언급. 소형 SMR 관련 언급과 함께 주가 하락에 대한 불만 표현.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['유상증자', '항암백신']</t>
+          <t>['원전', 'SMR', '주가 조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>81400</v>
+        <v>17530</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-6.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>605</v>
+        <v>240</v>
       </c>
       <c r="F22" t="n">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="G22" t="n">
-        <v>1757</v>
+        <v>981</v>
       </c>
       <c r="H22" t="n">
-        <v>23.03</v>
+        <v>10.38</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>86500</v>
+        <v>18800</v>
       </c>
       <c r="K22" t="n">
-        <v>86100</v>
+        <v>18800</v>
       </c>
       <c r="L22" t="n">
-        <v>86100</v>
+        <v>18800</v>
       </c>
       <c r="M22" t="n">
-        <v>80500</v>
+        <v>17370</v>
       </c>
       <c r="N22" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>263222416150</v>
+        <v>131275827590</v>
       </c>
       <c r="P22" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-486000</v>
+        <v>-2242000</v>
       </c>
       <c r="S22" t="n">
-        <v>-179000</v>
+        <v>-454000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국향 원전 수주 기대와 주가 하락에 대한 불만이 혼재된 의견.</t>
+          <t>공매도 세력의 파산 및 자금 오링 주장. 감사원 신고 및 정부 고위 인사 수사 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', 'SMR']</t>
+          <t>['공매도', '파산', '대차해지']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17530</v>
+        <v>2650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-6.76%</t>
+          <t>'-8.15%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.09</v>
+        <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>954</v>
+        <v>209</v>
       </c>
       <c r="H23" t="n">
-        <v>10.38</v>
+        <v>1.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>18800</v>
+        <v>2885</v>
       </c>
       <c r="K23" t="n">
-        <v>18800</v>
+        <v>3000</v>
       </c>
       <c r="L23" t="n">
-        <v>18800</v>
+        <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>17370</v>
+        <v>2645</v>
       </c>
       <c r="N23" t="n">
-        <v>10.47</v>
+        <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>128390120705</v>
+        <v>22246874297</v>
       </c>
       <c r="P23" t="n">
-        <v>40350</v>
+        <v>4760</v>
       </c>
       <c r="Q23" t="n">
-        <v>3320</v>
+        <v>973</v>
       </c>
       <c r="R23" t="n">
-        <v>-1898000</v>
+        <v>-199000</v>
       </c>
       <c r="S23" t="n">
-        <v>-250000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 및 마지막 몸부림에 대한 언급 다수.</t>
+          <t>셀리드 유상증자 및 경영권 변경 관련 해명 요구. 항암백신 AI 기업 뉴스 언급과 함께 주가 약세에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '주가조작']</t>
+          <t>['유상증자', '경영권 변경', '항암백신']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>299660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260923_13.xlsx
+++ b/data/trending_integrated_20260923_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4080</v>
+        <v>4095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.08%</t>
+          <t>'+23.53%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>36834827423</v>
+        <v>38081669024</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1943</v>
+        <v>1960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.21%</t>
+          <t>'+22.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
         <v>127</v>
@@ -702,7 +702,7 @@
         <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>49852945800</v>
+        <v>50969136190</v>
       </c>
       <c r="P3" t="n">
         <v>2465</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15470</v>
+        <v>15040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.73%</t>
+          <t>'+15.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.9</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
         <v>1.89</v>
@@ -794,7 +794,7 @@
         <v>2.79</v>
       </c>
       <c r="O4" t="n">
-        <v>94222385810</v>
+        <v>99836180015</v>
       </c>
       <c r="P4" t="n">
         <v>64600</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>초소형위성 자율 근접운영 국방과제 주관 및 67억원 규모 계약 체결. 테마 시작 기대감 속 단일가 매매 여부에 따른 주가 변동성 예상.</t>
+          <t>초소형위성 관련 국방과제 수주 사실을 바탕으로 우주 항공 대장주로의 성장을 기대하며 긍정적인 분위기를 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['초소형위성', '국방과제', '단일가']</t>
+          <t>['초소형위성', '우주항공']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="H5" t="n">
         <v>0.6</v>
@@ -886,7 +886,7 @@
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>87502904515</v>
+        <v>88867371685</v>
       </c>
       <c r="P5" t="n">
         <v>34650</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 11조원 포터블 X-Ray 시장 도전. 인도발 수주 및 미국, 인도, 인도네시아 시장 진출 재료로 인한 주가 상승 기대감.</t>
+          <t>스페이스X 및 NASA 선정, 인도발 수주 재료 등 다수의 호재를 바탕으로 10조원 규모의 휴대용 X-Ray 시장 선점 및 시총 1조원 돌파를 기대하고 있습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['X-Ray', '스페이스X', 'NASA']</t>
+          <t>['스페이스X', 'NASA', 'X-ray']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14530</v>
+        <v>14550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.77%</t>
+          <t>'+11.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H6" t="n">
         <v>0.86</v>
@@ -978,7 +978,7 @@
         <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>157856778230</v>
+        <v>158687540560</v>
       </c>
       <c r="P6" t="n">
         <v>25700</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18000</v>
+        <v>18010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+8.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F7" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>296485911605</v>
+        <v>297487846805</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식과 함께 엑스게이트의 양자 보안 관련 기대감 표현. 공매도 관련 언급.</t>
+          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자 보안', '아이온큐', '공매도']</t>
+          <t>['양자', '보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7890</v>
+        <v>219000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.42</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7610</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>7850</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>8720</v>
+        <v>220000</v>
       </c>
       <c r="M8" t="n">
-        <v>7730</v>
+        <v>216500</v>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>86668943535</v>
+        <v>791190701500</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>-26000</v>
+        <v>605000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
+          <t>배당금 증액 및 우선주 상승에 대한 기대감이 나타나며, 장기 보유를 통한 수익 창출을 희망하고 있습니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['계단식 하락', '매물대', '외인 매도']</t>
+          <t>['배당금', '우선주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,99 +1200,99 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219000</v>
+        <v>7820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+2.76%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="H9" t="n">
-        <v>75.51000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>211500</v>
+        <v>7610</v>
       </c>
       <c r="K9" t="n">
-        <v>217000</v>
+        <v>7850</v>
       </c>
       <c r="L9" t="n">
-        <v>220000</v>
+        <v>8720</v>
       </c>
       <c r="M9" t="n">
-        <v>216500</v>
+        <v>7730</v>
       </c>
       <c r="N9" t="n">
-        <v>75.5</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>773500417750</v>
+        <v>87622643075</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>16200</v>
       </c>
       <c r="Q9" t="n">
-        <v>65000</v>
+        <v>1206</v>
       </c>
       <c r="R9" t="n">
-        <v>605000</v>
+        <v>-26000</v>
       </c>
       <c r="S9" t="n">
-        <v>-57000</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
+          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '장기보유']</t>
+          <t>['계단식 하락', '매물대', '외인 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13980</v>
+        <v>13970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+2.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
         <v>205</v>
@@ -1346,7 +1346,7 @@
         <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>95402332020</v>
+        <v>95887692995</v>
       </c>
       <c r="P10" t="n">
         <v>23550</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>283500</v>
+        <v>284000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G11" t="n">
-        <v>1847</v>
+        <v>1839</v>
       </c>
       <c r="H11" t="n">
         <v>46.55</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3324488136500</v>
+        <v>3438295477250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 언급과 주가 관련 기대가 혼재된 의견.</t>
+          <t>대통령 관련 언급이 다수 포함되었으며, 주가 상승을 기대하는 개인 투자자들의 심리가 나타납니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1854000</v>
+        <v>1851000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,7 +1501,7 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G12" t="n">
         <v>1737</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3670862977500</v>
+        <v>3756292922500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 주식 시장의 신뢰 부족 및 정부 정책 비판. 미국 반도체 주가와 비교하며 SK하이닉스 주가 하락에 대한 불만 토로.</t>
+          <t>레버리지 및 국장 신뢰도 하락에 대한 불만을 표출하며, 반도체 섹터 전반의 부진에 대한 부정적인 인식을 드러냅니다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['국장', '정부 정책', '주가 조작']</t>
+          <t>['레버리지', '국장']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8530</v>
+        <v>8510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
         <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H13" t="n">
         <v>26.63</v>
@@ -1622,7 +1622,7 @@
         <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>22140012950</v>
+        <v>22475194350</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31450</v>
+        <v>31400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
         <v>52.79</v>
@@ -1714,7 +1714,7 @@
         <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>91646878075</v>
+        <v>92899274925</v>
       </c>
       <c r="P14" t="n">
         <v>32100</v>
@@ -1774,13 +1774,13 @@
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1806,7 +1806,7 @@
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>65719682972</v>
+        <v>66236379084</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미투온의 급격한 주가 하락 및 물량 떠넘기기에 대한 불만 표출. 상폐 가능성 및 국장 단타장 변질 비판.</t>
+          <t>주가 급락에 대한 불만과 단타성 거래에 대한 비판적인 시각이 나타나며, 상폐 가능성까지 언급하고 있습니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['물량 떠넘기기', '주포', '단타장']</t>
+          <t>['주가조작', '단타']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17630</v>
+        <v>30700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.01%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.76</v>
+        <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>125</v>
+        <v>296</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="G16" t="n">
-        <v>795</v>
+        <v>1914</v>
       </c>
       <c r="H16" t="n">
-        <v>5.46</v>
+        <v>16.63</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17810</v>
+        <v>31050</v>
       </c>
       <c r="K16" t="n">
-        <v>17950</v>
+        <v>31300</v>
       </c>
       <c r="L16" t="n">
-        <v>18180</v>
+        <v>31550</v>
       </c>
       <c r="M16" t="n">
-        <v>17410</v>
+        <v>30050</v>
       </c>
       <c r="N16" t="n">
-        <v>6.22</v>
+        <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>126699681050</v>
+        <v>10483446575</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>24150</v>
       </c>
       <c r="R16" t="n">
-        <v>-215000</v>
+        <v>-88000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
+          <t>간암 및 담관암 신약 FDA 승인 초읽기 및 글로벌 블록버스터 기대감이 고조되며, 공매도 세력에 대한 언급도 있습니다.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가', '명절', '단타']</t>
+          <t>['FDA', '신약', '간암']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30650</v>
+        <v>17590</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.24%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>285</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>1830</v>
+        <v>811</v>
       </c>
       <c r="H17" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K17" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L17" t="n">
-        <v>31550</v>
+        <v>18180</v>
       </c>
       <c r="M17" t="n">
-        <v>30050</v>
+        <v>17410</v>
       </c>
       <c r="N17" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O17" t="n">
-        <v>10237071875</v>
+        <v>129398606600</v>
       </c>
       <c r="P17" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-88000</v>
+        <v>-215000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>간암 및 담관암 신약 FDA 허가 초임박 소식과 함께 미국 릴레이테라퓨틱스 상승. 다만, CRL 가능성 및 공매도 이슈로 인한 주가 변동성 존재.</t>
+          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['FDA허가', '신약', '공매도']</t>
+          <t>['주가', '명절', '단타']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30950</v>
+        <v>30900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-2.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>72411223200</v>
+        <v>73543521100</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23050</v>
+        <v>23025</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H19" t="n">
         <v>1.68</v>
@@ -2174,7 +2174,7 @@
         <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>68849310150</v>
+        <v>69132691500</v>
       </c>
       <c r="P19" t="n">
         <v>39350</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48850</v>
+        <v>48900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.49%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H20" t="n">
         <v>38.34</v>
@@ -2266,7 +2266,7 @@
         <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>76142670250</v>
+        <v>77231029425</v>
       </c>
       <c r="P20" t="n">
         <v>67300</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81400</v>
+        <v>81500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-5.78%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="F21" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="G21" t="n">
-        <v>1779</v>
+        <v>1808</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>268387419700</v>
+        <v>271367617400</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17530</v>
+        <v>17520</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.76%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F22" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" t="n">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>131275827590</v>
+        <v>132272545700</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 및 자금 오링 주장. 감사원 신고 및 정부 고위 인사 수사 언급.</t>
+          <t>공매도 세력에 대한 강한 비난과 파산 가능성을 언급하며 주가 하락에 대한 부정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '파산', '대차해지']</t>
+          <t>['공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2650</v>
+        <v>2660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.15%</t>
+          <t>'-7.80%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G23" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2536,13 +2536,13 @@
         <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>2645</v>
+        <v>2630</v>
       </c>
       <c r="N23" t="n">
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22246874297</v>
+        <v>22356122997</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_13.xlsx
+++ b/data/trending_integrated_20260923_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4095</v>
+        <v>1962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.53%</t>
+          <t>'+22.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.02</v>
+        <v>-0.39</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H2" t="n">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3315</v>
+        <v>1603</v>
       </c>
       <c r="K2" t="n">
-        <v>3310</v>
+        <v>1603</v>
       </c>
       <c r="L2" t="n">
-        <v>4305</v>
+        <v>2030</v>
       </c>
       <c r="M2" t="n">
-        <v>3070</v>
+        <v>1585</v>
       </c>
       <c r="N2" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>38081669024</v>
+        <v>53288975169</v>
       </c>
       <c r="P2" t="n">
-        <v>6950</v>
+        <v>2465</v>
       </c>
       <c r="Q2" t="n">
-        <v>1809</v>
+        <v>865</v>
       </c>
       <c r="R2" t="n">
-        <v>-3000</v>
+        <v>-358000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3연상 기록, 엔트로픽 의료AI 관련 기대감 있으나 급락 가능성 언급. 개인 투자자 위주 거래.</t>
+          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['3연상', '의료AI', '개인매수']</t>
+          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>393210</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1960</v>
+        <v>4020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.27%</t>
+          <t>'+21.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.39</v>
+        <v>-1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1603</v>
+        <v>3315</v>
       </c>
       <c r="K3" t="n">
-        <v>1603</v>
+        <v>3310</v>
       </c>
       <c r="L3" t="n">
-        <v>2030</v>
+        <v>4305</v>
       </c>
       <c r="M3" t="n">
-        <v>1585</v>
+        <v>3070</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>50969136190</v>
+        <v>38839502420</v>
       </c>
       <c r="P3" t="n">
-        <v>2465</v>
+        <v>6950</v>
       </c>
       <c r="Q3" t="n">
-        <v>865</v>
+        <v>1809</v>
       </c>
       <c r="R3" t="n">
-        <v>-358000</v>
+        <v>-3000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈의 미국 특허 플렉시블 PCB, AI 데이터센터 공급 확대 뉴스 언급. ESS 및 NVIDIA 관련 기대감 표출.</t>
+          <t>3연상 기록, 엔트로픽 의료AI 관련 기대감 있으나 급락 가능성 언급. 개인 투자자 위주 거래.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['플렉시블 PCB', 'AI 데이터센터', '미국 특허']</t>
+          <t>['3연상', '의료AI', '개인매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>393210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15040</v>
+        <v>17970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.43%</t>
+          <t>'+15.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
         <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13030</v>
+        <v>15520</v>
       </c>
       <c r="K4" t="n">
-        <v>12850</v>
+        <v>15800</v>
       </c>
       <c r="L4" t="n">
-        <v>16420</v>
+        <v>19150</v>
       </c>
       <c r="M4" t="n">
-        <v>12660</v>
+        <v>15200</v>
       </c>
       <c r="N4" t="n">
-        <v>2.79</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>99836180015</v>
+        <v>91471822200</v>
       </c>
       <c r="P4" t="n">
-        <v>64600</v>
+        <v>34650</v>
       </c>
       <c r="Q4" t="n">
-        <v>7520</v>
+        <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>초소형위성 관련 국방과제 수주 사실을 바탕으로 우주 항공 대장주로의 성장을 기대하며 긍정적인 분위기를 보이고 있습니다.</t>
+          <t>스페이스X 선정 및 NASA 우주 임무 적합 장비 선정 기반의 포터블 X-Ray 시장 도전 및 주가 급등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['초소형위성', '우주항공']</t>
+          <t>['포터블 X-Ray', '스페이스X']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17720</v>
+        <v>14740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.18%</t>
+          <t>'+13.12%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15520</v>
+        <v>13030</v>
       </c>
       <c r="K5" t="n">
-        <v>15800</v>
+        <v>12850</v>
       </c>
       <c r="L5" t="n">
-        <v>19150</v>
+        <v>16420</v>
       </c>
       <c r="M5" t="n">
-        <v>15200</v>
+        <v>12660</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>2.79</v>
       </c>
       <c r="O5" t="n">
-        <v>88867371685</v>
+        <v>102019269830</v>
       </c>
       <c r="P5" t="n">
-        <v>34650</v>
+        <v>64600</v>
       </c>
       <c r="Q5" t="n">
-        <v>6980</v>
+        <v>7520</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 및 NASA 선정, 인도발 수주 재료 등 다수의 호재를 바탕으로 10조원 규모의 휴대용 X-Ray 시장 선점 및 시총 1조원 돌파를 기대하고 있습니다.</t>
+          <t>초소형 위성 국방과제 주관 및 우주 항공 테마 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', 'X-ray']</t>
+          <t>['초소형 위성']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14550</v>
+        <v>14540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.92%</t>
+          <t>'+11.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>0.86</v>
@@ -978,7 +978,7 @@
         <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>158687540560</v>
+        <v>159285122265</v>
       </c>
       <c r="P6" t="n">
         <v>25700</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18010</v>
+        <v>18070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.89%</t>
+          <t>'+9.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>297487846805</v>
+        <v>299619258645</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
+          <t>미국 양자 관련주 급등에 따른 주가 상승 기대 및 양자 보안 관련 기술 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자', '보안']</t>
+          <t>['양자 보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219000</v>
+        <v>7920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+4.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>368</v>
+        <v>312</v>
       </c>
       <c r="H8" t="n">
-        <v>75.51000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>7610</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>7850</v>
       </c>
       <c r="L8" t="n">
-        <v>220000</v>
+        <v>8720</v>
       </c>
       <c r="M8" t="n">
-        <v>216500</v>
+        <v>7730</v>
       </c>
       <c r="N8" t="n">
-        <v>75.5</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>791190701500</v>
+        <v>88429385805</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>65000</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>605000</v>
+        <v>-26000</v>
       </c>
       <c r="S8" t="n">
-        <v>-57000</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>배당금 증액 및 우선주 상승에 대한 기대감이 나타나며, 장기 보유를 통한 수익 창출을 희망하고 있습니다.</t>
+          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당금', '우선주']</t>
+          <t>['계단식 하락', '매물대', '외인 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7820</v>
+        <v>219500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.42</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7610</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>7850</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>8720</v>
+        <v>220000</v>
       </c>
       <c r="M9" t="n">
-        <v>7730</v>
+        <v>216500</v>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>87622643075</v>
+        <v>811425685750</v>
       </c>
       <c r="P9" t="n">
-        <v>16200</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1206</v>
+        <v>65000</v>
       </c>
       <c r="R9" t="n">
-        <v>-26000</v>
+        <v>605000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
+          <t>배당금 증액 및 우선주 상승에 대한 기대감이 나타나며, 장기 보유를 통한 수익 창출을 희망하고 있습니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['계단식 하락', '매물대', '외인 매도']</t>
+          <t>['배당금', '우선주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13970</v>
+        <v>13990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.72%</t>
+          <t>'+2.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H10" t="n">
         <v>9.609999999999999</v>
@@ -1346,7 +1346,7 @@
         <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>95887692995</v>
+        <v>96584620780</v>
       </c>
       <c r="P10" t="n">
         <v>23550</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>284000</v>
+        <v>283750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>489</v>
       </c>
       <c r="G11" t="n">
-        <v>1839</v>
+        <v>1810</v>
       </c>
       <c r="H11" t="n">
         <v>46.55</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3438295477250</v>
+        <v>3535367684500</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대통령 관련 언급이 다수 포함되었으며, 주가 상승을 기대하는 개인 투자자들의 심리가 나타납니다.</t>
+          <t>주가 상승 및 하락에 대한 상반된 전망과 정치 관련 언급이 혼재된 게시글.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G12" t="n">
-        <v>1737</v>
+        <v>1729</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3756292922500</v>
+        <v>3844157431000</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8510</v>
+        <v>3730</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+0.13%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-0.35</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>342</v>
+        <v>413</v>
       </c>
       <c r="H13" t="n">
-        <v>26.63</v>
+        <v>0.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8470</v>
+        <v>3725</v>
       </c>
       <c r="K13" t="n">
-        <v>8510</v>
+        <v>3740</v>
       </c>
       <c r="L13" t="n">
-        <v>8870</v>
+        <v>4200</v>
       </c>
       <c r="M13" t="n">
-        <v>8480</v>
+        <v>3705</v>
       </c>
       <c r="N13" t="n">
-        <v>26.58</v>
+        <v>0.96</v>
       </c>
       <c r="O13" t="n">
-        <v>22475194350</v>
+        <v>66432422454</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>6300</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>1738</v>
       </c>
       <c r="R13" t="n">
-        <v>275000</v>
+        <v>-191000</v>
       </c>
       <c r="S13" t="n">
-        <v>-45000</v>
+        <v>-5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LG디스플레이 유리기판 사업 및 게이밍 OLED 관련 신규 기술 언급. 일부 투자자 매수세 유입 및 목표가 상향 기대.</t>
+          <t>주가 급락에 대한 불만과 물량 떠넘기기에 대한 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유리기판', 'OLED', '커스텀 공정']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31400</v>
+        <v>8480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="H14" t="n">
-        <v>52.79</v>
+        <v>26.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,152 +1699,152 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31400</v>
+        <v>8470</v>
       </c>
       <c r="K14" t="n">
-        <v>31500</v>
+        <v>8510</v>
       </c>
       <c r="L14" t="n">
-        <v>32100</v>
+        <v>8870</v>
       </c>
       <c r="M14" t="n">
-        <v>31100</v>
+        <v>8480</v>
       </c>
       <c r="N14" t="n">
-        <v>25.75</v>
+        <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>92899274925</v>
+        <v>23268944715</v>
       </c>
       <c r="P14" t="n">
-        <v>32100</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>21000</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-37000</v>
+        <v>275000</v>
       </c>
       <c r="S14" t="n">
-        <v>174000</v>
+        <v>-45000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>키움증권의 매매 행태 분석과 유리 기판, 게이밍 OLED 등 신사업 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['유리 기판', '게이밍 OLED']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3720</v>
+        <v>31400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.13%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.35</v>
+        <v>0.62</v>
       </c>
       <c r="E15" t="n">
+        <v>52</v>
+      </c>
+      <c r="F15" t="n">
+        <v>34</v>
+      </c>
+      <c r="G15" t="n">
         <v>148</v>
       </c>
-      <c r="F15" t="n">
-        <v>79</v>
-      </c>
-      <c r="G15" t="n">
-        <v>406</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.61</v>
+        <v>52.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3725</v>
+        <v>31400</v>
       </c>
       <c r="K15" t="n">
-        <v>3740</v>
+        <v>31500</v>
       </c>
       <c r="L15" t="n">
-        <v>4200</v>
+        <v>32100</v>
       </c>
       <c r="M15" t="n">
-        <v>3705</v>
+        <v>31100</v>
       </c>
       <c r="N15" t="n">
-        <v>0.96</v>
+        <v>25.75</v>
       </c>
       <c r="O15" t="n">
-        <v>66236379084</v>
+        <v>93697161600</v>
       </c>
       <c r="P15" t="n">
-        <v>6300</v>
+        <v>32100</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>21000</v>
       </c>
       <c r="R15" t="n">
-        <v>-191000</v>
+        <v>-37000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>174000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 불만과 단타성 거래에 대한 비판적인 시각이 나타나며, 상폐 가능성까지 언급하고 있습니다.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가조작', '단타']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30700</v>
+        <v>30650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F16" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G16" t="n">
-        <v>1914</v>
+        <v>1967</v>
       </c>
       <c r="H16" t="n">
         <v>16.63</v>
@@ -1898,7 +1898,7 @@
         <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>10483446575</v>
+        <v>10604368100</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>간암 및 담관암 신약 FDA 승인 초읽기 및 글로벌 블록버스터 기대감이 고조되며, 공매도 세력에 대한 언급도 있습니다.</t>
+          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암/담관암 신약 FDA 허가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA', '신약', '간암']</t>
+          <t>['신약 허가', 'FDA']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17590</v>
+        <v>17510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.24%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="H17" t="n">
         <v>5.46</v>
@@ -1990,7 +1990,7 @@
         <v>6.22</v>
       </c>
       <c r="O17" t="n">
-        <v>129398606600</v>
+        <v>131460434085</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2056,7 +2056,7 @@
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>73543521100</v>
+        <v>74243890850</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23025</v>
+        <v>48850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.86%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G19" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>38.34</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23950</v>
+        <v>51200</v>
       </c>
       <c r="K19" t="n">
-        <v>24400</v>
+        <v>51600</v>
       </c>
       <c r="L19" t="n">
-        <v>25700</v>
+        <v>51600</v>
       </c>
       <c r="M19" t="n">
-        <v>23000</v>
+        <v>48600</v>
       </c>
       <c r="N19" t="n">
-        <v>1.76</v>
+        <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>69132691500</v>
+        <v>78526530425</v>
       </c>
       <c r="P19" t="n">
-        <v>39350</v>
+        <v>67300</v>
       </c>
       <c r="Q19" t="n">
-        <v>8200</v>
+        <v>23150</v>
       </c>
       <c r="R19" t="n">
-        <v>-53000</v>
+        <v>-327000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>타임지 세계 최고 헬스테크 기업 선정 및 반지 재료 부각. 매수세 부진과 거래량 감소 속 추세선에 따른 방향성 결정 예상.</t>
+          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '반지']</t>
+          <t>['20일선', '주가 하락', 'MSCI']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48900</v>
+        <v>22850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.49%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="H20" t="n">
-        <v>38.34</v>
+        <v>1.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51200</v>
+        <v>23950</v>
       </c>
       <c r="K20" t="n">
-        <v>51600</v>
+        <v>24400</v>
       </c>
       <c r="L20" t="n">
-        <v>51600</v>
+        <v>25700</v>
       </c>
       <c r="M20" t="n">
-        <v>48600</v>
+        <v>22700</v>
       </c>
       <c r="N20" t="n">
-        <v>38.44</v>
+        <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>77231029425</v>
+        <v>71252769250</v>
       </c>
       <c r="P20" t="n">
-        <v>67300</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>23150</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>-327000</v>
+        <v>-53000</v>
       </c>
       <c r="S20" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
+          <t>타임지 세계 최고 헬스테크 기업 선정 및 반지 재료 부각. 매수세 부진과 거래량 감소 속 추세선에 따른 방향성 결정 예상.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['20일선', '주가 하락', 'MSCI']</t>
+          <t>['헬스테크', '타임지', '반지']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81500</v>
+        <v>81400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.78%</t>
+          <t>'-5.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="F21" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="G21" t="n">
-        <v>1808</v>
+        <v>1843</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>271367617400</v>
+        <v>277477041650</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17520</v>
+        <v>2685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-6.93%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.09</v>
+        <v>0.92</v>
       </c>
       <c r="E22" t="n">
-        <v>243</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>997</v>
+        <v>230</v>
       </c>
       <c r="H22" t="n">
-        <v>10.38</v>
+        <v>1.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>18800</v>
+        <v>2885</v>
       </c>
       <c r="K22" t="n">
-        <v>18800</v>
+        <v>3000</v>
       </c>
       <c r="L22" t="n">
-        <v>18800</v>
+        <v>3480</v>
       </c>
       <c r="M22" t="n">
-        <v>17370</v>
+        <v>2630</v>
       </c>
       <c r="N22" t="n">
-        <v>10.47</v>
+        <v>0.48</v>
       </c>
       <c r="O22" t="n">
-        <v>132272545700</v>
+        <v>22509846067</v>
       </c>
       <c r="P22" t="n">
-        <v>40350</v>
+        <v>4760</v>
       </c>
       <c r="Q22" t="n">
-        <v>3320</v>
+        <v>973</v>
       </c>
       <c r="R22" t="n">
-        <v>-2242000</v>
+        <v>-199000</v>
       </c>
       <c r="S22" t="n">
-        <v>-454000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비난과 파산 가능성을 언급하며 주가 하락에 대한 부정적인 전망을 보이고 있습니다.</t>
+          <t>유상증자 및 경영권 변경 관련 이슈와 항암백신 AI 기업으로의 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작']</t>
+          <t>['유상증자', '항암백신']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2660</v>
+        <v>17410</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.80%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="E23" t="n">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="G23" t="n">
-        <v>212</v>
+        <v>1011</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4</v>
+        <v>10.38</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2885</v>
+        <v>18800</v>
       </c>
       <c r="K23" t="n">
-        <v>3000</v>
+        <v>18800</v>
       </c>
       <c r="L23" t="n">
-        <v>3480</v>
+        <v>18800</v>
       </c>
       <c r="M23" t="n">
-        <v>2630</v>
+        <v>17370</v>
       </c>
       <c r="N23" t="n">
-        <v>0.48</v>
+        <v>10.47</v>
       </c>
       <c r="O23" t="n">
-        <v>22356122997</v>
+        <v>134943496135</v>
       </c>
       <c r="P23" t="n">
-        <v>4760</v>
+        <v>40350</v>
       </c>
       <c r="Q23" t="n">
-        <v>973</v>
+        <v>3320</v>
       </c>
       <c r="R23" t="n">
-        <v>-199000</v>
+        <v>-2242000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-454000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>셀리드 유상증자 및 경영권 변경 관련 해명 요구. 항암백신 AI 기업 뉴스 언급과 함께 주가 약세에 대한 불만 표출.</t>
+          <t>공매도 세력에 대한 강한 비난과 파산 가능성을 언급하며 주가 하락에 대한 부정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['유상증자', '경영권 변경', '항암백신']</t>
+          <t>['공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260923_13.xlsx
+++ b/data/trending_integrated_20260923_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.39</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H2" t="n">
         <v>1.02</v>
@@ -610,7 +610,7 @@
         <v>1.41</v>
       </c>
       <c r="O2" t="n">
-        <v>53288975169</v>
+        <v>54582743446</v>
       </c>
       <c r="P2" t="n">
         <v>2465</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4020</v>
+        <v>3955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.27%</t>
+          <t>'+19.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.02</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
         <v>1.63</v>
@@ -702,7 +702,7 @@
         <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>38839502420</v>
+        <v>40344544195</v>
       </c>
       <c r="P3" t="n">
         <v>6950</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17970</v>
+        <v>17800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.79%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H4" t="n">
         <v>0.6</v>
@@ -794,7 +794,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>91471822200</v>
+        <v>92384617725</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14740</v>
+        <v>14450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.12%</t>
+          <t>'+11.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G5" t="n">
         <v>105</v>
       </c>
-      <c r="F5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>84</v>
-      </c>
       <c r="H5" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13030</v>
+        <v>13000</v>
       </c>
       <c r="K5" t="n">
-        <v>12850</v>
+        <v>12870</v>
       </c>
       <c r="L5" t="n">
-        <v>16420</v>
+        <v>15900</v>
       </c>
       <c r="M5" t="n">
-        <v>12660</v>
+        <v>12650</v>
       </c>
       <c r="N5" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>102019269830</v>
+        <v>160552954165</v>
       </c>
       <c r="P5" t="n">
-        <v>64600</v>
+        <v>25700</v>
       </c>
       <c r="Q5" t="n">
-        <v>7520</v>
+        <v>4600</v>
       </c>
       <c r="R5" t="n">
-        <v>2000</v>
+        <v>84000</v>
       </c>
       <c r="S5" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>초소형 위성 국방과제 주관 및 우주 항공 테마 상승 기대감.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['초소형 위성']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14540</v>
+        <v>14450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.85%</t>
+          <t>'+10.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13000</v>
+        <v>13030</v>
       </c>
       <c r="K6" t="n">
-        <v>12870</v>
+        <v>12850</v>
       </c>
       <c r="L6" t="n">
-        <v>15900</v>
+        <v>16420</v>
       </c>
       <c r="M6" t="n">
-        <v>12650</v>
+        <v>12660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>159285122265</v>
+        <v>106449252910</v>
       </c>
       <c r="P6" t="n">
-        <v>25700</v>
+        <v>64600</v>
       </c>
       <c r="Q6" t="n">
-        <v>4600</v>
+        <v>7520</v>
       </c>
       <c r="R6" t="n">
-        <v>84000</v>
+        <v>2000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['나라스페이스', '초소형위성', '우주항공']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18070</v>
+        <v>18100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.25%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G7" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>299619258645</v>
+        <v>300697683675</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 주가 상승 기대 및 양자 보안 관련 기술 언급.</t>
+          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자 보안']</t>
+          <t>['양자', '보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7920</v>
+        <v>219500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.07%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.42</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7610</v>
+        <v>211500</v>
       </c>
       <c r="K8" t="n">
-        <v>7850</v>
+        <v>217000</v>
       </c>
       <c r="L8" t="n">
-        <v>8720</v>
+        <v>220000</v>
       </c>
       <c r="M8" t="n">
-        <v>7730</v>
+        <v>216500</v>
       </c>
       <c r="N8" t="n">
-        <v>2.32</v>
+        <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>88429385805</v>
+        <v>836159328500</v>
       </c>
       <c r="P8" t="n">
-        <v>16200</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1206</v>
+        <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>-26000</v>
+        <v>605000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>-57000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>우리로의 계단식 하락 및 매물대 소화 과정 언급. 외인 매도 정리 후 주가 상승 기대.</t>
+          <t>평생 보유 및 수천만원대 배당금 수령에 대한 기대감이 높음. 우선주 소각 이슈와 자사주 관련 언급이 있음.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['계단식 하락', '매물대', '외인 매도']</t>
+          <t>['우선주', '배당금', '자사주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219500</v>
+        <v>7880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.78%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="H9" t="n">
-        <v>75.51000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>211500</v>
+        <v>7610</v>
       </c>
       <c r="K9" t="n">
-        <v>217000</v>
+        <v>7850</v>
       </c>
       <c r="L9" t="n">
-        <v>220000</v>
+        <v>8720</v>
       </c>
       <c r="M9" t="n">
-        <v>216500</v>
+        <v>7730</v>
       </c>
       <c r="N9" t="n">
-        <v>75.5</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>811425685750</v>
+        <v>88878405040</v>
       </c>
       <c r="P9" t="n">
-        <v>243500</v>
+        <v>16200</v>
       </c>
       <c r="Q9" t="n">
-        <v>65000</v>
+        <v>1206</v>
       </c>
       <c r="R9" t="n">
-        <v>605000</v>
+        <v>-26000</v>
       </c>
       <c r="S9" t="n">
-        <v>-57000</v>
+        <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>배당금 증액 및 우선주 상승에 대한 기대감이 나타나며, 장기 보유를 통한 수익 창출을 희망하고 있습니다.</t>
+          <t>대표의 계단식 하락 유도 및 지독한 매도에 대한 불만이 제기됨. 실체 있는 기업이라는 긍정적 언급과 과열 우려가 공존함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당금', '우선주']</t>
+          <t>['우리로', '양자', '빛샘']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13990</v>
+        <v>13980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>9.77</v>
       </c>
       <c r="O10" t="n">
-        <v>96584620780</v>
+        <v>97169540455</v>
       </c>
       <c r="P10" t="n">
         <v>23550</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>283750</v>
+        <v>284000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G11" t="n">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H11" t="n">
         <v>46.55</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>3535367684500</v>
+        <v>3582084334750</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 상승 및 하락에 대한 상반된 전망과 정치 관련 언급이 혼재된 게시글.</t>
+          <t>정치적 언급과 함께 주가 상승 및 하락 전망이 혼재됨. 개인 투자자들의 매수/매도 및 배당 관련 문의가 존재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1851000</v>
+        <v>1852000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+0.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G12" t="n">
-        <v>1729</v>
+        <v>1701</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>3844157431000</v>
+        <v>3915323863500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>레버리지 및 국장 신뢰도 하락에 대한 불만을 표출하며, 반도체 섹터 전반의 부진에 대한 부정적인 인식을 드러냅니다.</t>
+          <t>주가 관리 부실 및 레버리지 영향으로 인한 하락세에 대한 불만이 고조됨. 정부 정책 비판과 함께 해외 반도체 주가와의 비교가 언급됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['레버리지', '국장']</t>
+          <t>['SK하이닉스', '레버리지', 'ADR']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3730</v>
+        <v>8490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.13%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.35</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="H13" t="n">
-        <v>0.61</v>
+        <v>26.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3725</v>
+        <v>8470</v>
       </c>
       <c r="K13" t="n">
-        <v>3740</v>
+        <v>8510</v>
       </c>
       <c r="L13" t="n">
-        <v>4200</v>
+        <v>8870</v>
       </c>
       <c r="M13" t="n">
-        <v>3705</v>
+        <v>8470</v>
       </c>
       <c r="N13" t="n">
-        <v>0.96</v>
+        <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>66432422454</v>
+        <v>24165041945</v>
       </c>
       <c r="P13" t="n">
-        <v>6300</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>1738</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-191000</v>
+        <v>275000</v>
       </c>
       <c r="S13" t="n">
-        <v>-5000</v>
+        <v>-45000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 불만과 물량 떠넘기기에 대한 의혹 제기.</t>
+          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['LG디스플레이', '유리기판', 'OLED']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8480</v>
+        <v>31450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>346</v>
+        <v>149</v>
       </c>
       <c r="H14" t="n">
-        <v>26.63</v>
+        <v>52.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,130 +1699,130 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>31400</v>
       </c>
       <c r="K14" t="n">
-        <v>8510</v>
+        <v>31500</v>
       </c>
       <c r="L14" t="n">
-        <v>8870</v>
+        <v>32100</v>
       </c>
       <c r="M14" t="n">
-        <v>8480</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58</v>
+        <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>23268944715</v>
+        <v>95515454525</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>32100</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R14" t="n">
-        <v>275000</v>
+        <v>-37000</v>
       </c>
       <c r="S14" t="n">
-        <v>-45000</v>
+        <v>174000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>키움증권의 매매 행태 분석과 유리 기판, 게이밍 OLED 등 신사업 관련 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유리 기판', '게이밍 OLED']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31400</v>
+        <v>3695</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.81%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.62</v>
+        <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="G15" t="n">
-        <v>148</v>
+        <v>442</v>
       </c>
       <c r="H15" t="n">
-        <v>52.8</v>
+        <v>0.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>31400</v>
+        <v>3725</v>
       </c>
       <c r="K15" t="n">
-        <v>31500</v>
+        <v>3740</v>
       </c>
       <c r="L15" t="n">
-        <v>32100</v>
+        <v>4200</v>
       </c>
       <c r="M15" t="n">
-        <v>31100</v>
+        <v>3685</v>
       </c>
       <c r="N15" t="n">
-        <v>25.75</v>
+        <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>93697161600</v>
+        <v>67142545386</v>
       </c>
       <c r="P15" t="n">
-        <v>32100</v>
+        <v>6300</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-37000</v>
+        <v>-191000</v>
       </c>
       <c r="S15" t="n">
-        <v>174000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만이 제기됨. 상폐 가능성 및 단타 위주의 거래에 대한 부정적 인식이 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F16" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G16" t="n">
-        <v>1967</v>
+        <v>2007</v>
       </c>
       <c r="H16" t="n">
         <v>16.63</v>
@@ -1898,7 +1898,7 @@
         <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>10604368100</v>
+        <v>10853348525</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 릴레이테라퓨틱스 주가 상승 및 간암/담관암 신약 FDA 허가 기대감.</t>
+          <t>미국 릴라이테라퓨틱스 상승 및 FDA 승인 기대감, 간암/담관암 결과 발표 대기 중. HLB 담관암 신약 FDA 허가 임박 소식.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신약 허가', 'FDA']</t>
+          <t>['FDA', '릴라이테라퓨틱스', '신약']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17510</v>
+        <v>17540</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.68%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G17" t="n">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="H17" t="n">
         <v>5.46</v>
@@ -1990,7 +1990,7 @@
         <v>6.22</v>
       </c>
       <c r="O17" t="n">
-        <v>131460434085</v>
+        <v>133952573755</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>명절 전 주가 상승 기대와 단타 세력에 대한 언급.</t>
+          <t>추석 전 2만원 돌파 기대감과 함께 쇼티지 및 급등 가능성이 언급됨. 주포의 움직임 및 단타 세력에 대한 의견이 존재함.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가', '명절', '단타']</t>
+          <t>['대한광통신', '광통신', '쇼티지']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30900</v>
+        <v>31100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.22%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>74243890850</v>
+        <v>75402257400</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48850</v>
+        <v>48900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
         <v>70</v>
       </c>
       <c r="G19" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
         <v>38.34</v>
@@ -2174,7 +2174,7 @@
         <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>78526530425</v>
+        <v>79381694275</v>
       </c>
       <c r="P19" t="n">
         <v>67300</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22850</v>
+        <v>22800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-4.80%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H20" t="n">
         <v>1.68</v>
@@ -2266,7 +2266,7 @@
         <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>71252769250</v>
+        <v>71765780700</v>
       </c>
       <c r="P20" t="n">
         <v>39350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>타임지 세계 최고 헬스테크 기업 선정 및 반지 재료 부각. 매수세 부진과 거래량 감소 속 추세선에 따른 방향성 결정 예상.</t>
+          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '반지']</t>
+          <t>['헬스테크', '타임지', '거래량']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81400</v>
+        <v>81300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="F21" t="n">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="G21" t="n">
-        <v>1843</v>
+        <v>1869</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>277477041650</v>
+        <v>280963490100</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 한국형 원전 2기 확정 소식 언급. 소형 SMR 관련 언급과 함께 주가 하락에 대한 불만 표현.</t>
+          <t>한국형 원전 2기 수주 확정 등 호재 언급과 함께 차트 붕괴 및 주가 하락에 대한 불안감이 공존함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가 조작']</t>
+          <t>['원전', 'SMR', '차트']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2685</v>
+        <v>17440</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.93%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.92</v>
+        <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>254</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="G22" t="n">
-        <v>230</v>
+        <v>1041</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4</v>
+        <v>10.38</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2885</v>
+        <v>18800</v>
       </c>
       <c r="K22" t="n">
-        <v>3000</v>
+        <v>18800</v>
       </c>
       <c r="L22" t="n">
-        <v>3480</v>
+        <v>18800</v>
       </c>
       <c r="M22" t="n">
-        <v>2630</v>
+        <v>17370</v>
       </c>
       <c r="N22" t="n">
-        <v>0.48</v>
+        <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>22509846067</v>
+        <v>138509898315</v>
       </c>
       <c r="P22" t="n">
-        <v>4760</v>
+        <v>40350</v>
       </c>
       <c r="Q22" t="n">
-        <v>973</v>
+        <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-199000</v>
+        <v>-2242000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-454000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>유상증자 및 경영권 변경 관련 이슈와 항암백신 AI 기업으로의 전환 가능성 언급.</t>
+          <t>공매도 세력에 대한 강한 비난과 파산 가능성을 언급하며 주가 하락에 대한 부정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['유상증자', '항암백신']</t>
+          <t>['공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17410</v>
+        <v>2670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.39%</t>
+          <t>'-7.45%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.09</v>
+        <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>1011</v>
+        <v>237</v>
       </c>
       <c r="H23" t="n">
-        <v>10.38</v>
+        <v>1.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>18800</v>
+        <v>2885</v>
       </c>
       <c r="K23" t="n">
-        <v>18800</v>
+        <v>3000</v>
       </c>
       <c r="L23" t="n">
-        <v>18800</v>
+        <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>17370</v>
+        <v>2630</v>
       </c>
       <c r="N23" t="n">
-        <v>10.47</v>
+        <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>134943496135</v>
+        <v>22594593067</v>
       </c>
       <c r="P23" t="n">
-        <v>40350</v>
+        <v>4760</v>
       </c>
       <c r="Q23" t="n">
-        <v>3320</v>
+        <v>973</v>
       </c>
       <c r="R23" t="n">
-        <v>-2242000</v>
+        <v>-199000</v>
       </c>
       <c r="S23" t="n">
-        <v>-454000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 강한 비난과 파산 가능성을 언급하며 주가 하락에 대한 부정적인 전망을 보이고 있습니다.</t>
+          <t>유상증자 및 경영권 변경 관련 의혹과 함께 주가 하락에 대한 부정적 의견이 지배적임. 항암백신 AI 기업이라는 긍정적 언급도 일부 존재함.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작']</t>
+          <t>['셀리드', '유상증자', '항암백신']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
